--- a/outputs/식이_개발전달_20260923/maiReport_식이_개발전달_데이터계약_v1.2.0.xlsx
+++ b/outputs/식이_개발전달_20260923/maiReport_식이_개발전달_데이터계약_v1.2.0.xlsx
@@ -2,31 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Re525a84018904f61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테이블정의" sheetId="2" r:id="Rab4c7c21bc214337"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="필드정의" sheetId="3" r:id="R91a0c860237f4cc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정필요" sheetId="4" r:id="Re8afd30da270431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질문" sheetId="5" r:id="R82fd906a9f204118"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="선택지" sheetId="6" r:id="Rba935555f1424c8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="목표문구" sheetId="7" r:id="R72d5ce9fa51f46b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="노출조건" sheetId="8" r:id="R50d60f508dd74391"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환규칙" sheetId="9" r:id="R264969744a9d4929"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환연결축" sheetId="10" r:id="Rd695b3d183dd4170"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환금지성격" sheetId="11" r:id="R518650eed9c34569"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드조건" sheetId="12" r:id="R4ce54de066734de3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정" sheetId="13" r:id="Rb720b9eb3cf44c7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정파라미터" sheetId="14" r:id="Ra591d036a7264160"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진출처" sheetId="15" r:id="Rb826433b24ef4ce2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진항목" sheetId="16" r:id="R8b460b24617a44dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진성분규격" sheetId="17" r:id="Ra96d313c27bb42eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진판정그룹" sheetId="18" r:id="Rc2c781210cb84143"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진판정조건" sheetId="19" r:id="R6fa471771ab2464e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진범주코드" sheetId="20" r:id="R223ef02d292e4227"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진적용정책" sheetId="21" r:id="R9974eeb807f248bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진보조기준" sheetId="22" r:id="R108bf8cf413f4dc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진식이연결" sheetId="23" r:id="R0f0f3a2f5ef14eff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="또래등수정책" sheetId="24" r:id="Rf5c8e96a25bc4191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검증규칙" sheetId="25" r:id="Rf55c8c07da6d4b96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Rf546fbc6cd0d4bbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테이블정의" sheetId="2" r:id="Rb8373bfe374a42dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="필드정의" sheetId="3" r:id="R295b853deaf6472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정필요" sheetId="4" r:id="R2e9322906bcd4ff8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질문" sheetId="5" r:id="R0b28f0497b964947"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="선택지" sheetId="6" r:id="Re991702abdfe417e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="목표문구" sheetId="7" r:id="R8433d32876d745f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="노출조건" sheetId="8" r:id="Ra72c6af34bd94b27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환규칙" sheetId="9" r:id="Rbbc304611be14241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환연결축" sheetId="10" r:id="Rf62bf522236b4b18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환금지성격" sheetId="11" r:id="Rf08af250be1a4610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드조건" sheetId="12" r:id="R0ca81c1bf6a34797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정" sheetId="13" r:id="R5abb4cd18c1b4c79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정파라미터" sheetId="14" r:id="R932fc9d233184767"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진출처" sheetId="15" r:id="Ra896824ffb5b4212"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진항목" sheetId="16" r:id="R67456f5626ae4472"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진성분규격" sheetId="17" r:id="Rbe8550782a324f85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진판정그룹" sheetId="18" r:id="Rc9a3340e84014079"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진판정조건" sheetId="19" r:id="Re854392076f04d31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진범주코드" sheetId="20" r:id="Ra497bd21ff4742ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진적용정책" sheetId="21" r:id="R24609182b5d3441a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진보조기준" sheetId="22" r:id="Re632277297424b89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진식이연결" sheetId="23" r:id="R0d8122d5a3294b7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="또래등수정책" sheetId="24" r:id="R1a173768f80d4647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검증규칙" sheetId="25" r:id="R1704a7ce80f94f7d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -859,7 +859,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R824941725f724fdc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99d1079c49d5430d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1066,7 +1066,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e7c2ed9dbe04e77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree9b83b6a55f4779"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1394,7 +1394,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2af74fa488dc41de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R196efb362a42403d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3475,7 +3475,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffd6413cb61c4859"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16bb169af7cb40f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5161,7 +5161,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R518122f7118d4771"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10f4690667e94a30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5572,7 +5572,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2668c0ee42a4913"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re13b5ff55b094235"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5751,7 +5751,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6225328909e4171"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc46516407a434606"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6188,7 +6188,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73ee4dcd21d44296"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R744749dca6834b80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6549,7 +6549,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce25777029634bec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96cb8e6ffafd4d6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8141,7 +8141,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f87c2a27e074e4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f50e4bfb3ae43da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9721,7 +9721,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R514bd10fe0444ef6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47ebe5035c574001"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10527,7 +10527,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd642f9b53e04347"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2814aef6c4544dbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10617,7 +10617,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7057a2f438a44998"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdec3595eb85b40dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10820,7 +10820,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c424efe86644e1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb62d0cdbd1924f52"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11677,7 +11677,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R543959bdb5394175"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf749fd75bf3f431a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11824,7 +11824,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d2daece05924aaf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0328b6e59dbe4879"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12017,7 +12017,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b34fc43c8424205"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R425e8fc40a0b4d57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12430,7 +12430,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R408616699f584642"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R603340e7e410460f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19016,7 +19016,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d52f75513674567"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree8dbd30c06c4d71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19523,7 +19523,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd45fa5433f2b4323"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3736c6cffba48c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19810,7 +19810,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d4e5da473e34307"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40552e91da804608"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20395,7 +20395,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc093b4f2e454440d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52e878339bbe4c0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27134,7 +27134,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R390adf3db2aa4716"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f534ff73b4f47c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28219,7 +28219,7 @@
         <x:v>WEEKEND</x:v>
       </x:c>
       <x:c r="F36" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="G36" s="9" t="b">
         <x:v>0</x:v>
@@ -28227,9 +28227,7 @@
       <x:c r="H36" s="6" t="str">
         <x:v>READY</x:v>
       </x:c>
-      <x:c r="I36" s="2" t="str">
-        <x:v>ONE</x:v>
-      </x:c>
+      <x:c r="I36" s="2"/>
       <x:c r="J36" s="2"/>
       <x:c r="K36" s="2" t="n">
         <x:v>36</x:v>
@@ -29186,7 +29184,7 @@
         <x:v>WEEKDAY</x:v>
       </x:c>
       <x:c r="F67" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="G67" s="9" t="b">
         <x:v>0</x:v>
@@ -29194,9 +29192,7 @@
       <x:c r="H67" s="6" t="str">
         <x:v>READY</x:v>
       </x:c>
-      <x:c r="I67" s="2" t="str">
-        <x:v>ONE</x:v>
-      </x:c>
+      <x:c r="I67" s="2"/>
       <x:c r="J67" s="2"/>
       <x:c r="K67" s="2" t="n">
         <x:v>67</x:v>
@@ -29317,7 +29313,7 @@
         <x:v>EVENING</x:v>
       </x:c>
       <x:c r="E71" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="F71" s="2" t="str">
         <x:v>COMPANY_DINNER</x:v>
@@ -29326,7 +29322,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H71" s="6" t="str">
-        <x:v>NEED_CONTEXT_CALENDAR</x:v>
+        <x:v>NEED_CONTEXT</x:v>
       </x:c>
       <x:c r="I71" s="2" t="str">
         <x:v>ONE</x:v>
@@ -29802,7 +29798,7 @@
         <x:v>EVENING</x:v>
       </x:c>
       <x:c r="E86" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="F86" s="2" t="str">
         <x:v>COMPANY_DINNER</x:v>
@@ -29811,7 +29807,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H86" s="6" t="str">
-        <x:v>NEED_CONTEXT_CALENDAR</x:v>
+        <x:v>NEED_CONTEXT</x:v>
       </x:c>
       <x:c r="I86" s="2" t="str">
         <x:v>ONE</x:v>
@@ -30291,7 +30287,7 @@
         <x:v>MORNING_ENTRY</x:v>
       </x:c>
       <x:c r="E101" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="F101" s="2" t="str">
         <x:v>TRAVEL</x:v>
@@ -30300,7 +30296,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H101" s="6" t="str">
-        <x:v>NEED_CONTEXT_CALENDAR</x:v>
+        <x:v>NEED_CONTEXT</x:v>
       </x:c>
       <x:c r="I101" s="2" t="str">
         <x:v>ONE</x:v>
@@ -30326,7 +30322,7 @@
         <x:v>EVENING</x:v>
       </x:c>
       <x:c r="E102" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="F102" s="2" t="str">
         <x:v>OVERTIME</x:v>
@@ -30335,7 +30331,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H102" s="6" t="str">
-        <x:v>NEED_CONTEXT_CALENDAR</x:v>
+        <x:v>NEED_CONTEXT</x:v>
       </x:c>
       <x:c r="I102" s="2" t="str">
         <x:v>ONE</x:v>
@@ -30358,13 +30354,13 @@
         <x:v>명절 · 연휴</x:v>
       </x:c>
       <x:c r="D103" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="E103" s="2" t="str">
         <x:v>HOLIDAY_OR_EXTENDED</x:v>
       </x:c>
       <x:c r="F103" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="G103" s="9" t="b">
         <x:v>0</x:v>
@@ -30372,9 +30368,7 @@
       <x:c r="H103" s="6" t="str">
         <x:v>NEED_CALENDAR</x:v>
       </x:c>
-      <x:c r="I103" s="2" t="str">
-        <x:v>ONE</x:v>
-      </x:c>
+      <x:c r="I103" s="2"/>
       <x:c r="J103" s="2"/>
       <x:c r="K103" s="2" t="n">
         <x:v>103</x:v>
@@ -30492,10 +30486,10 @@
         <x:v>편의점 · 배달</x:v>
       </x:c>
       <x:c r="D107" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="E107" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="F107" s="2" t="str">
         <x:v>MULTI</x:v>
@@ -30504,7 +30498,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H107" s="6" t="str">
-        <x:v>NEED_CONTEXT_CALENDAR</x:v>
+        <x:v>NEED_CONTEXT</x:v>
       </x:c>
       <x:c r="I107" s="2" t="str">
         <x:v>ANY_OF</x:v>
@@ -30663,7 +30657,7 @@
         <x:v>명절 · 회식</x:v>
       </x:c>
       <x:c r="D112" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="E112" s="2" t="str">
         <x:v>HOLIDAY</x:v>
@@ -30957,7 +30951,7 @@
         <x:v>EVENING</x:v>
       </x:c>
       <x:c r="E121" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="F121" s="2" t="str">
         <x:v>OVERTIME</x:v>
@@ -30966,7 +30960,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H121" s="6" t="str">
-        <x:v>NEED_CONTEXT_CALENDAR</x:v>
+        <x:v>NEED_CONTEXT</x:v>
       </x:c>
       <x:c r="I121" s="2" t="str">
         <x:v>ONE</x:v>
@@ -31026,7 +31020,7 @@
         <x:v>WEEKEND</x:v>
       </x:c>
       <x:c r="F123" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="G123" s="9" t="b">
         <x:v>0</x:v>
@@ -31034,9 +31028,7 @@
       <x:c r="H123" s="6" t="str">
         <x:v>READY</x:v>
       </x:c>
-      <x:c r="I123" s="2" t="str">
-        <x:v>ONE</x:v>
-      </x:c>
+      <x:c r="I123" s="2"/>
       <x:c r="J123" s="2"/>
       <x:c r="K123" s="2" t="n">
         <x:v>123</x:v>
@@ -31088,7 +31080,7 @@
         <x:v>명절 · 뷔페</x:v>
       </x:c>
       <x:c r="D125" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="E125" s="2" t="str">
         <x:v>HOLIDAY</x:v>
@@ -31126,7 +31118,7 @@
         <x:v>EVENING</x:v>
       </x:c>
       <x:c r="E126" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="F126" s="2" t="str">
         <x:v>COMPANY_DINNER</x:v>
@@ -31135,7 +31127,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H126" s="6" t="str">
-        <x:v>NEED_CONTEXT_CALENDAR</x:v>
+        <x:v>NEED_CONTEXT</x:v>
       </x:c>
       <x:c r="I126" s="2" t="str">
         <x:v>ONE</x:v>
@@ -31460,7 +31452,7 @@
         <x:v>EVENING</x:v>
       </x:c>
       <x:c r="E136" s="2" t="str">
-        <x:v>UNKNOWN</x:v>
+        <x:v>ANY</x:v>
       </x:c>
       <x:c r="F136" s="2" t="str">
         <x:v>COMPANY_DINNER</x:v>
@@ -31469,7 +31461,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H136" s="6" t="str">
-        <x:v>NEED_CONTEXT_CALENDAR</x:v>
+        <x:v>NEED_CONTEXT</x:v>
       </x:c>
       <x:c r="I136" s="2" t="str">
         <x:v>ONE</x:v>
@@ -32755,7 +32747,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref4de992affc4be7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a163ca01f9d4dc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33286,7 +33278,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1890941aa8e4e30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c426532fe0747bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>